--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -66,7 +66,7 @@
     <x:t>Amateur</x:t>
   </x:si>
   <x:si>
-    <x:t>EDISSA  ABASTAS AMANTE</x:t>
+    <x:t>EDISSA ABASTAS AMANTE</x:t>
   </x:si>
   <x:si>
     <x:t>Manimpis, City Of San Fernando (Capital), Pampanga</x:t>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -9,58 +9,22 @@
     <x:sheet name="June 2025" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -196,7 +160,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -223,12 +187,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -236,6 +194,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -250,13 +229,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -301,12 +273,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -318,14 +290,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -507,7 +479,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -518,183 +490,201 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -958,488 +948,464 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45832.3271759259</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>45832.3271990741</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>16854</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>45832.3384259259</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
         <x:v>45825.0450347222</x:v>
       </x:c>
-      <x:c r="I7" s="12">
+      <x:c r="I7" s="17">
         <x:v>45825.0450578704</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="16" t="n">
         <x:v>1546810</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="K7" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="17">
         <x:v>45825.0561574074</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="16" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s"/>
+      <x:c r="E8" s="19" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H8" s="20">
         <x:v>45827.2810416667</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="20">
         <x:v>45827.2810648148</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="n">
+      <x:c r="J8" s="19" t="n">
         <x:v>1616</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="21" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="18">
+      <x:c r="L8" s="20">
         <x:v>45827.2917592593</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M8" s="19" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
+      <x:c r="B9" s="19" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s"/>
+      <x:c r="E9" s="19" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
         <x:v>45826.3109259259</x:v>
       </x:c>
-      <x:c r="I9" s="16">
+      <x:c r="I9" s="20">
         <x:v>45826.3109375</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="n">
+      <x:c r="J9" s="19" t="n">
         <x:v>1432235</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="21" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="20">
         <x:v>45826.3168865741</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>31</x:v>
+      <x:c r="M9" s="19" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="B10" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s"/>
+      <x:c r="E10" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
         <x:v>45825.5009259259</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="13">
         <x:v>45825.5010185185</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="12" t="n">
         <x:v>1434267</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="15">
         <x:v>45827.2850694444</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>31</x:v>
+      <x:c r="M10" s="11" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="B11" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
         <x:v>45825.1485185185</x:v>
       </x:c>
-      <x:c r="I11" s="16">
+      <x:c r="I11" s="13">
         <x:v>45825.1485416667</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="12" t="n">
         <x:v>15135861</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="14" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="15">
         <x:v>45825.1676388889</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M11" s="11" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="B12" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
         <x:v>45827.0419791667</x:v>
       </x:c>
-      <x:c r="I12" s="16">
+      <x:c r="I12" s="13">
         <x:v>45827.0420138889</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="12" t="n">
         <x:v>52268</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="14" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="15">
         <x:v>45827.0460069444</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M12" s="11" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="B13" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="I13" s="22">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="12" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="14" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="15">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M13" s="11" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
+      <x:c r="B16" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="25" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
-        <x:v>53</x:v>
+      <x:c r="B17" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="B18" s="29" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="B19" s="29" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="B20" s="29" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="B21" s="29" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="B22" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="B23" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="29" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
+      <x:c r="B24" s="32" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C24" s="33" t="s"/>
+      <x:c r="D24" s="33" t="s"/>
+      <x:c r="E24" s="33" t="s"/>
+      <x:c r="F24" s="34" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -22,9 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
-  <x:si>
-    <x:t>{{Name}}</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+  <x:si>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EVALUATOR3 EDGE</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -933,7 +936,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -950,7 +955,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45809</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -1013,20 +1018,20 @@
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>45832.3271759259</x:v>
@@ -1044,7 +1049,7 @@
         <x:v>45832.3384259259</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -1052,20 +1057,20 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="16" t="s"/>
       <x:c r="E7" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G7" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H7" s="17">
         <x:v>45825.0450347222</x:v>
@@ -1083,27 +1088,27 @@
         <x:v>45825.0561574074</x:v>
       </x:c>
       <x:c r="M7" s="16" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="19" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="19" t="s"/>
       <x:c r="E8" s="19" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F8" s="19" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="19" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="20">
         <x:v>45827.2810416667</x:v>
@@ -1121,25 +1126,25 @@
         <x:v>45827.2917592593</x:v>
       </x:c>
       <x:c r="M8" s="19" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D9" s="19" t="s"/>
       <x:c r="E9" s="19" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="19" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G9" s="19" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H9" s="20">
         <x:v>45826.3109259259</x:v>
@@ -1157,25 +1162,25 @@
         <x:v>45826.3168865741</x:v>
       </x:c>
       <x:c r="M9" s="19" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="11" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="11" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D10" s="12" t="s"/>
       <x:c r="E10" s="11" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F10" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G10" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H10" s="13">
         <x:v>45825.5009259259</x:v>
@@ -1193,27 +1198,27 @@
         <x:v>45827.2850694444</x:v>
       </x:c>
       <x:c r="M10" s="11" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="11" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D11" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E11" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F11" s="11" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G11" s="11" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H11" s="13">
         <x:v>45825.1485185185</x:v>
@@ -1231,27 +1236,27 @@
         <x:v>45825.1676388889</x:v>
       </x:c>
       <x:c r="M11" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="11" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C12" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D12" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E12" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F12" s="11" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G12" s="11" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H12" s="13">
         <x:v>45827.0419791667</x:v>
@@ -1269,27 +1274,27 @@
         <x:v>45827.0460069444</x:v>
       </x:c>
       <x:c r="M12" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="11" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="11" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D13" s="12" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E13" s="11" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F13" s="11" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G13" s="11" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H13" s="13">
         <x:v>45827.1931712963</x:v>
@@ -1307,78 +1312,58 @@
         <x:v>45827.2195833333</x:v>
       </x:c>
       <x:c r="M13" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="25" t="s"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="25" t="s"/>
     </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="s">
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="26" t="s">
         <x:v>41</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="29" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C19" s="30" t="s"/>
-      <x:c r="D19" s="30" t="s"/>
-      <x:c r="E19" s="30" t="s"/>
-      <x:c r="F19" s="31" t="n">
-        <x:v>2</x:v>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="s">
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="29" t="s">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C20" s="30" t="s"/>
       <x:c r="D20" s="30" t="s"/>
       <x:c r="E20" s="30" t="s"/>
       <x:c r="F20" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="29" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C21" s="30" t="s"/>
       <x:c r="D21" s="30" t="s"/>
       <x:c r="E21" s="30" t="s"/>
       <x:c r="F21" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C22" s="30" t="s"/>
       <x:c r="D22" s="30" t="s"/>
@@ -1389,7 +1374,7 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="29" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C23" s="30" t="s"/>
       <x:c r="D23" s="30" t="s"/>
@@ -1398,19 +1383,39 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="32" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="s"/>
-      <x:c r="D24" s="33" t="s"/>
-      <x:c r="E24" s="33" t="s"/>
-      <x:c r="F24" s="34" t="n">
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="29" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="29" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="s"/>
+      <x:c r="D25" s="30" t="s"/>
+      <x:c r="E25" s="30" t="s"/>
+      <x:c r="F25" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B26" s="32" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C26" s="33" t="s"/>
+      <x:c r="D26" s="33" t="s"/>
+      <x:c r="E26" s="33" t="s"/>
+      <x:c r="F26" s="34" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2379,18 +2384,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+  <x:mergeCells count="12">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -560,7 +560,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -596,6 +596,50 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -615,32 +659,12 @@
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1016,7 +1040,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
@@ -1054,7 +1078,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>2</x:v>
@@ -1166,253 +1190,279 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+      <x:c r="B10" s="22" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
+      <x:c r="C10" s="22" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s"/>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="D10" s="23" t="s"/>
+      <x:c r="E10" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="F10" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="G10" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="H10" s="24">
         <x:v>45825.5009259259</x:v>
       </x:c>
-      <x:c r="I10" s="13">
+      <x:c r="I10" s="24">
         <x:v>45825.5010185185</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="23" t="n">
         <x:v>1434267</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="25" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="26">
         <x:v>45827.2850694444</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
+      <x:c r="M10" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
+      <x:c r="B11" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="s">
+      <x:c r="C11" s="22" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="s">
+      <x:c r="D11" s="23" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="E11" s="22" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="F11" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="G11" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="H11" s="24">
         <x:v>45825.1485185185</x:v>
       </x:c>
-      <x:c r="I11" s="13">
+      <x:c r="I11" s="24">
         <x:v>45825.1485416667</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="23" t="n">
         <x:v>15135861</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="K11" s="25" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="L11" s="15">
+      <x:c r="L11" s="26">
         <x:v>45825.1676388889</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
+      <x:c r="M11" s="22" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="s">
+      <x:c r="C12" s="22" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="s">
+      <x:c r="D12" s="23" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="s">
+      <x:c r="E12" s="22" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="s">
+      <x:c r="F12" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="s">
+      <x:c r="G12" s="22" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H12" s="13">
+      <x:c r="H12" s="24">
         <x:v>45827.0419791667</x:v>
       </x:c>
-      <x:c r="I12" s="13">
+      <x:c r="I12" s="24">
         <x:v>45827.0420138889</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="n">
+      <x:c r="J12" s="23" t="n">
         <x:v>52268</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="n">
+      <x:c r="K12" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="15">
+      <x:c r="L12" s="26">
         <x:v>45827.0460069444</x:v>
       </x:c>
-      <x:c r="M12" s="11" t="s">
+      <x:c r="M12" s="22" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="s">
+      <x:c r="C13" s="22" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="s">
+      <x:c r="D13" s="23" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="s">
+      <x:c r="E13" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="s">
+      <x:c r="F13" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="s">
+      <x:c r="G13" s="22" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H13" s="13">
+      <x:c r="H13" s="24">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I13" s="22">
+      <x:c r="I13" s="27">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="n">
+      <x:c r="J13" s="23" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="n">
+      <x:c r="K13" s="25" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L13" s="15">
+      <x:c r="L13" s="26">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M13" s="11" t="s">
+      <x:c r="M13" s="22" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B14" s="28" t="s"/>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="28" t="s"/>
+      <x:c r="G14" s="28" t="s"/>
+      <x:c r="H14" s="28" t="s"/>
+      <x:c r="I14" s="28" t="s"/>
+      <x:c r="J14" s="28" t="s"/>
+      <x:c r="K14" s="28" t="s"/>
+      <x:c r="L14" s="28" t="s"/>
+      <x:c r="M14" s="28" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B15" s="28" t="s"/>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="28" t="s"/>
+      <x:c r="G15" s="28" t="s"/>
+      <x:c r="H15" s="28" t="s"/>
+      <x:c r="I15" s="28" t="s"/>
+      <x:c r="J15" s="28" t="s"/>
+      <x:c r="K15" s="28" t="s"/>
+      <x:c r="L15" s="28" t="s"/>
+      <x:c r="M15" s="28" t="s"/>
+    </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="23" t="s">
+      <x:c r="B18" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="25" t="s"/>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="31" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+      <x:c r="B19" s="32" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="s">
+      <x:c r="C19" s="33" t="s"/>
+      <x:c r="D19" s="33" t="s"/>
+      <x:c r="E19" s="33" t="s"/>
+      <x:c r="F19" s="34" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="29" t="s">
+      <x:c r="B20" s="35" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
+      <x:c r="C20" s="36" t="s"/>
+      <x:c r="D20" s="36" t="s"/>
+      <x:c r="E20" s="36" t="s"/>
+      <x:c r="F20" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="29" t="s">
+      <x:c r="B21" s="35" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
+      <x:c r="C21" s="36" t="s"/>
+      <x:c r="D21" s="36" t="s"/>
+      <x:c r="E21" s="36" t="s"/>
+      <x:c r="F21" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="29" t="s">
+      <x:c r="B22" s="35" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C22" s="30" t="s"/>
-      <x:c r="D22" s="30" t="s"/>
-      <x:c r="E22" s="30" t="s"/>
-      <x:c r="F22" s="31" t="n">
+      <x:c r="C22" s="36" t="s"/>
+      <x:c r="D22" s="36" t="s"/>
+      <x:c r="E22" s="36" t="s"/>
+      <x:c r="F22" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="29" t="s">
+      <x:c r="B23" s="35" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
+      <x:c r="C23" s="36" t="s"/>
+      <x:c r="D23" s="36" t="s"/>
+      <x:c r="E23" s="36" t="s"/>
+      <x:c r="F23" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="29" t="s">
+      <x:c r="B24" s="35" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
+      <x:c r="C24" s="36" t="s"/>
+      <x:c r="D24" s="36" t="s"/>
+      <x:c r="E24" s="36" t="s"/>
+      <x:c r="F24" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="29" t="s">
+      <x:c r="B25" s="35" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C25" s="30" t="s"/>
-      <x:c r="D25" s="30" t="s"/>
-      <x:c r="E25" s="30" t="s"/>
-      <x:c r="F25" s="31" t="n">
+      <x:c r="C25" s="36" t="s"/>
+      <x:c r="D25" s="36" t="s"/>
+      <x:c r="E25" s="36" t="s"/>
+      <x:c r="F25" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="32" t="s">
+      <x:c r="B26" s="38" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C26" s="33" t="s"/>
-      <x:c r="D26" s="33" t="s"/>
-      <x:c r="E26" s="33" t="s"/>
-      <x:c r="F26" s="34" t="n">
+      <x:c r="C26" s="39" t="s"/>
+      <x:c r="D26" s="39" t="s"/>
+      <x:c r="E26" s="39" t="s"/>
+      <x:c r="F26" s="40" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -1010,7 +1010,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1078,7 +1078,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>2</x:v>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -22,12 +22,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>EVALUATOR3 EDGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -163,7 +199,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -208,21 +244,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -232,6 +253,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -482,7 +510,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -493,74 +521,68 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -591,56 +613,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -655,63 +629,75 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1012,18 +998,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1041,428 +1015,440 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45832.3384259259</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="I7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>7</x:v>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s"/>
-      <x:c r="E8" s="19" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H8" s="20">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I8" s="20">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J8" s="19" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45832.3271759259</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45832.3271990741</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>16854</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="20">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>7</x:v>
+      <x:c r="L8" s="12">
+        <x:v>45832.3384259259</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s"/>
-      <x:c r="E9" s="19" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
+      <x:c r="B9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I9" s="20">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J9" s="19" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K9" s="21" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="22" t="s">
+      <x:c r="B10" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C10" s="22" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D10" s="23" t="s"/>
-      <x:c r="E10" s="22" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F10" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G10" s="22" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H10" s="24">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I10" s="24">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J10" s="23" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K10" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L10" s="26">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M10" s="22" t="s">
-        <x:v>20</x:v>
+      <x:c r="F10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="23" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E11" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F11" s="22" t="s">
+      <x:c r="B11" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G11" s="22" t="s">
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H11" s="24">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I11" s="24">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J11" s="23" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K11" s="25" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L11" s="26">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M11" s="22" t="s">
-        <x:v>7</x:v>
+      <x:c r="F11" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45826.3109259259</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>45826.3109375</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1432235</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>45826.3168865741</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D12" s="23" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E12" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F12" s="22" t="s">
+      <x:c r="B12" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45825.5009259259</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>45825.5010185185</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1434267</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>45827.2850694444</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="G12" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H12" s="24">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I12" s="24">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J12" s="23" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K12" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="26">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M12" s="22" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D13" s="23" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E13" s="22" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F13" s="22" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G13" s="22" t="s">
+      <x:c r="C13" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H13" s="24">
+      <x:c r="E13" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45825.1485185185</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>45825.1485416667</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>15135861</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>45825.1676388889</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I13" s="27">
+      <x:c r="I15" s="19">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J13" s="23" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K13" s="25" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L13" s="26">
+      <x:c r="L15" s="18">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M13" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B14" s="28" t="s"/>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="28" t="s"/>
-      <x:c r="G14" s="28" t="s"/>
-      <x:c r="H14" s="28" t="s"/>
-      <x:c r="I14" s="28" t="s"/>
-      <x:c r="J14" s="28" t="s"/>
-      <x:c r="K14" s="28" t="s"/>
-      <x:c r="L14" s="28" t="s"/>
-      <x:c r="M14" s="28" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B15" s="28" t="s"/>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="28" t="s"/>
-      <x:c r="G15" s="28" t="s"/>
-      <x:c r="H15" s="28" t="s"/>
-      <x:c r="I15" s="28" t="s"/>
-      <x:c r="J15" s="28" t="s"/>
-      <x:c r="K15" s="28" t="s"/>
-      <x:c r="L15" s="28" t="s"/>
-      <x:c r="M15" s="28" t="s"/>
+      <x:c r="M15" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="31" t="s"/>
+      <x:c r="B18" s="20" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="32" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="s"/>
-      <x:c r="D19" s="33" t="s"/>
-      <x:c r="E19" s="33" t="s"/>
-      <x:c r="F19" s="34" t="s">
-        <x:v>42</x:v>
+      <x:c r="B19" s="23" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="35" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="36" t="s"/>
-      <x:c r="D20" s="36" t="s"/>
-      <x:c r="E20" s="36" t="s"/>
-      <x:c r="F20" s="37" t="n">
+      <x:c r="B20" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="35" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C21" s="36" t="s"/>
-      <x:c r="D21" s="36" t="s"/>
-      <x:c r="E21" s="36" t="s"/>
-      <x:c r="F21" s="37" t="n">
+      <x:c r="B21" s="26" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="35" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C22" s="36" t="s"/>
-      <x:c r="D22" s="36" t="s"/>
-      <x:c r="E22" s="36" t="s"/>
-      <x:c r="F22" s="37" t="n">
+      <x:c r="B22" s="26" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="35" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C23" s="36" t="s"/>
-      <x:c r="D23" s="36" t="s"/>
-      <x:c r="E23" s="36" t="s"/>
-      <x:c r="F23" s="37" t="n">
+      <x:c r="B23" s="26" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="35" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C24" s="36" t="s"/>
-      <x:c r="D24" s="36" t="s"/>
-      <x:c r="E24" s="36" t="s"/>
-      <x:c r="F24" s="37" t="n">
+      <x:c r="B24" s="26" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="35" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C25" s="36" t="s"/>
-      <x:c r="D25" s="36" t="s"/>
-      <x:c r="E25" s="36" t="s"/>
-      <x:c r="F25" s="37" t="n">
+      <x:c r="B25" s="26" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="38" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C26" s="39" t="s"/>
-      <x:c r="D26" s="39" t="s"/>
-      <x:c r="E26" s="39" t="s"/>
-      <x:c r="F26" s="40" t="n">
+      <x:c r="B26" s="29" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C26" s="30" t="s"/>
+      <x:c r="D26" s="30" t="s"/>
+      <x:c r="E26" s="30" t="s"/>
+      <x:c r="F26" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -22,12 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>EVALUATOR3 EDGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -199,7 +202,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -239,6 +242,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -510,14 +537,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -530,59 +566,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -613,91 +649,103 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -926,58 +974,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1020,435 +1068,435 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45832.3271759259</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>45832.3271990741</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>16854</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45832.3384259259</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I9" s="12">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K9" s="13" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="12">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="B10" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="C10" s="17" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="G10" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>45827.2810416667</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="19">
         <x:v>45827.2810648148</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1616</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="21">
         <x:v>45827.2917592593</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="B11" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="17" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="F11" s="17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="G11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
         <x:v>45826.3109259259</x:v>
       </x:c>
-      <x:c r="I11" s="16">
+      <x:c r="I11" s="19">
         <x:v>45826.3109375</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>1432235</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="21">
         <x:v>45826.3168865741</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>32</x:v>
+      <x:c r="M11" s="17" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="B12" s="17" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="17" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>45825.5009259259</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>45825.5010185185</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1434267</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>45827.2850694444</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="B13" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>45825.1485185185</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>45825.1485416667</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>15135861</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>45825.1676388889</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="B14" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="C14" s="17" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="D14" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="G14" s="17" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
         <x:v>45827.0419791667</x:v>
       </x:c>
-      <x:c r="I14" s="16">
+      <x:c r="I14" s="19">
         <x:v>45827.0420138889</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J14" s="18" t="n">
         <x:v>52268</x:v>
       </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="K14" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="18">
+      <x:c r="L14" s="21">
         <x:v>45827.0460069444</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M14" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="B15" s="17" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
+      <x:c r="C15" s="17" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="D15" s="18" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="E15" s="17" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="F15" s="17" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H15" s="16">
+      <x:c r="G15" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="I15" s="22">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J15" s="18" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="K15" s="20" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L15" s="18">
+      <x:c r="L15" s="21">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M15" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
+      <x:c r="B18" s="23" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="25" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="B19" s="26" t="s">
         <x:v>54</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="s">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="B20" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="B21" s="29" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="B22" s="29" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="B23" s="29" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="B24" s="29" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="B25" s="29" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="s"/>
+      <x:c r="D25" s="30" t="s"/>
+      <x:c r="E25" s="30" t="s"/>
+      <x:c r="F25" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="29" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C26" s="30" t="s"/>
-      <x:c r="D26" s="30" t="s"/>
-      <x:c r="E26" s="30" t="s"/>
-      <x:c r="F26" s="31" t="n">
+      <x:c r="B26" s="32" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C26" s="33" t="s"/>
+      <x:c r="D26" s="33" t="s"/>
+      <x:c r="E26" s="33" t="s"/>
+      <x:c r="F26" s="34" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2423,7 +2471,7 @@
   <x:mergeCells count="12">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -67,6 +67,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -199,10 +235,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -247,15 +285,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -271,15 +301,8 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -542,21 +565,21 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -566,59 +589,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -649,103 +672,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -974,78 +985,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1066,7 +1089,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1106,402 +1129,452 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45832.3384259259</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
       <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
+      <x:c r="B10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>45832.3271759259</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45832.3271990741</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>16854</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L10" s="19">
+        <x:v>45832.3384259259</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
+      <x:c r="B11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>33</x:v>
+      <x:c r="F12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
+      <x:c r="B13" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G13" s="17" t="s">
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H13" s="19">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="F13" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>45826.3109259259</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45826.3109375</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1432235</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>45826.3168865741</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
+      <x:c r="B14" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s"/>
+      <x:c r="E14" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>45825.5009259259</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>45825.5010185185</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1434267</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>45827.2850694444</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
+      <x:c r="B15" s="15" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G15" s="17" t="s">
+      <x:c r="C15" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H15" s="19">
+      <x:c r="E15" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>45825.1485185185</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>45825.1485416667</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>15135861</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>45825.1676388889</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I15" s="22">
+      <x:c r="I17" s="17">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J15" s="18" t="n">
+      <x:c r="J17" s="16" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K15" s="20" t="n">
+      <x:c r="K17" s="18" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L15" s="21">
+      <x:c r="L17" s="19">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="M17" s="15" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="25" t="s"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="20" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C20" s="21" t="s"/>
+      <x:c r="D20" s="21" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="22" t="s"/>
     </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="29" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
-        <x:v>2</x:v>
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="23" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C21" s="24" t="s"/>
+      <x:c r="D21" s="24" t="s"/>
+      <x:c r="E21" s="24" t="s"/>
+      <x:c r="F21" s="25" t="s">
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C22" s="30" t="s"/>
-      <x:c r="D22" s="30" t="s"/>
-      <x:c r="E22" s="30" t="s"/>
-      <x:c r="F22" s="31" t="n">
-        <x:v>1</x:v>
+      <x:c r="B22" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="29" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
-        <x:v>1</x:v>
+      <x:c r="B23" s="26" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="29" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
+      <x:c r="B24" s="26" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="29" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C25" s="30" t="s"/>
-      <x:c r="D25" s="30" t="s"/>
-      <x:c r="E25" s="30" t="s"/>
-      <x:c r="F25" s="31" t="n">
+      <x:c r="B25" s="26" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="32" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="s"/>
-      <x:c r="D26" s="33" t="s"/>
-      <x:c r="E26" s="33" t="s"/>
-      <x:c r="F26" s="34" t="n">
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="26" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="26" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B28" s="29" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C28" s="30" t="s"/>
+      <x:c r="D28" s="30" t="s"/>
+      <x:c r="E28" s="30" t="s"/>
+      <x:c r="F28" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2468,19 +2541,20 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="12">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="13">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -67,42 +67,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -240,7 +204,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -284,14 +248,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -303,6 +259,21 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -560,7 +531,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -568,16 +539,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -589,13 +560,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -607,41 +572,50 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -672,28 +646,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -708,55 +674,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1089,7 +1071,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1129,452 +1111,402 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45832.3271759259</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45832.3271990741</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>16854</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45832.3384259259</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+      <x:c r="H9" s="15">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="G10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="H10" s="19">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45832.3384259259</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="L10" s="21">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="B11" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>45826.3109259259</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>45826.3109375</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1432235</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>45826.3168865741</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="17" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="17" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="G12" s="17" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="H12" s="19">
+        <x:v>45825.5009259259</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>45825.5010185185</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1434267</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>45827.2850694444</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="B13" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="G13" s="17" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>45</x:v>
+      <x:c r="H13" s="19">
+        <x:v>45825.1485185185</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>45825.1485416667</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>15135861</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>45825.1676388889</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>45</x:v>
+      <x:c r="H14" s="19">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="G15" s="17" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="H15" s="19">
+        <x:v>45827.1931712963</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>44197</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1234312</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>18810</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>45827.2195833333</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="22" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="24" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="25" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H15" s="17">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="s">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>32</x:v>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>45827.1931712963</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>44197</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1234312</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>18810</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>45827.2195833333</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="20" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C20" s="21" t="s"/>
-      <x:c r="D20" s="21" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="22" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="s">
-        <x:v>67</x:v>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="28" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C21" s="29" t="s"/>
+      <x:c r="D21" s="29" t="s"/>
+      <x:c r="E21" s="29" t="s"/>
+      <x:c r="F21" s="30" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
-        <x:v>2</x:v>
+      <x:c r="B22" s="28" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C22" s="29" t="s"/>
+      <x:c r="D22" s="29" t="s"/>
+      <x:c r="E22" s="29" t="s"/>
+      <x:c r="F22" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>2</x:v>
+      <x:c r="B23" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="B24" s="28" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C24" s="29" t="s"/>
+      <x:c r="D24" s="29" t="s"/>
+      <x:c r="E24" s="29" t="s"/>
+      <x:c r="F24" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="B25" s="28" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C25" s="29" t="s"/>
+      <x:c r="D25" s="29" t="s"/>
+      <x:c r="E25" s="29" t="s"/>
+      <x:c r="F25" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
-        <x:v>1</x:v>
+    <x:row r="26" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B26" s="31" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C26" s="32" t="s"/>
+      <x:c r="D26" s="32" t="s"/>
+      <x:c r="E26" s="32" t="s"/>
+      <x:c r="F26" s="33" t="n">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B28" s="29" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C28" s="30" t="s"/>
-      <x:c r="D28" s="30" t="s"/>
-      <x:c r="E28" s="30" t="s"/>
-      <x:c r="F28" s="31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2546,15 +2478,15 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B20:F20"/>
+    <x:mergeCell ref="B18:F18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
-    <x:mergeCell ref="B28:E28"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -84,6 +84,9 @@
     <x:t>61-6-2025-1061</x:t>
   </x:si>
   <x:si>
+    <x:t>16854</x:t>
+  </x:si>
+  <x:si>
     <x:t>cashier3 edge</x:t>
   </x:si>
   <x:si>
@@ -99,6 +102,9 @@
     <x:t>61-6-2025-1003</x:t>
   </x:si>
   <x:si>
+    <x:t>1546810</x:t>
+  </x:si>
+  <x:si>
     <x:t>Radiotelegraphy</x:t>
   </x:si>
   <x:si>
@@ -111,6 +117,9 @@
     <x:t>61-6-2025-1054</x:t>
   </x:si>
   <x:si>
+    <x:t>1616</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDWARD LANCE LORILLA</x:t>
   </x:si>
   <x:si>
@@ -123,6 +132,9 @@
     <x:t>61-6-2025-1025</x:t>
   </x:si>
   <x:si>
+    <x:t>1432235</x:t>
+  </x:si>
+  <x:si>
     <x:t>MANUELITO TOLENTINO</x:t>
   </x:si>
   <x:si>
@@ -141,6 +153,9 @@
     <x:t>61-6-2025-1012</x:t>
   </x:si>
   <x:si>
+    <x:t>1434267</x:t>
+  </x:si>
+  <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
   </x:si>
   <x:si>
@@ -153,6 +168,9 @@
     <x:t>61-6-2025-1005</x:t>
   </x:si>
   <x:si>
+    <x:t>15135861</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -165,6 +183,10 @@
     <x:t>61-6-2025-1050</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">
+52268</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -181,6 +203,9 @@
   </x:si>
   <x:si>
     <x:t>61-6-2025-1052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234312</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -204,7 +229,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -273,13 +298,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -531,7 +549,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -572,50 +590,41 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -663,6 +672,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -674,71 +687,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1119,7 +1116,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1129,23 +1126,23 @@
       <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="H8" s="16">
+        <x:v>45832.3271846875</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45832.3272087963</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45832.3384259259</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45832.3384320023</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -1153,355 +1150,355 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45825.0450396991</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45825.0450687153</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>45825.0561645718</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45827.2810495602</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45827.2810737963</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45827.2917648032</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45826.310926169</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>45826.3109462384</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>33</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45826.3168925232</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
+      <x:c r="B12" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45825.5009313657</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>45825.5010245718</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>45827.2850752315</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
+      <x:c r="B13" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45825.1485242593</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>45825.1485531713</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>45825.1676413542</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
+    <x:row r="14" spans="1:28" ht="33.597656" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="E14" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45827.0419894213</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>45827.0420140278</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="21">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L14" s="18">
+        <x:v>45827.0460181713</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>45827.1931712963</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="B15" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>45827.193172581</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1234312</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
+      <x:c r="J15" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L15" s="21">
-        <x:v>45827.2195833333</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L15" s="18">
+        <x:v>45827.2195876273</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s"/>
-      <x:c r="D18" s="23" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="24" t="s"/>
+      <x:c r="B18" s="19" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="s"/>
+      <x:c r="D18" s="20" t="s"/>
+      <x:c r="E18" s="21" t="s"/>
+      <x:c r="F18" s="21" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="s">
-        <x:v>55</x:v>
+      <x:c r="B19" s="22" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="28" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="28" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C21" s="29" t="s"/>
-      <x:c r="D21" s="29" t="s"/>
-      <x:c r="E21" s="29" t="s"/>
-      <x:c r="F21" s="30" t="n">
+      <x:c r="B21" s="25" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="28" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C22" s="29" t="s"/>
-      <x:c r="D22" s="29" t="s"/>
-      <x:c r="E22" s="29" t="s"/>
-      <x:c r="F22" s="30" t="n">
+      <x:c r="B22" s="25" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="28" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C23" s="29" t="s"/>
-      <x:c r="D23" s="29" t="s"/>
-      <x:c r="E23" s="29" t="s"/>
-      <x:c r="F23" s="30" t="n">
+      <x:c r="B23" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="28" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C24" s="29" t="s"/>
-      <x:c r="D24" s="29" t="s"/>
-      <x:c r="E24" s="29" t="s"/>
-      <x:c r="F24" s="30" t="n">
+      <x:c r="B24" s="25" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="28" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C25" s="29" t="s"/>
-      <x:c r="D25" s="29" t="s"/>
-      <x:c r="E25" s="29" t="s"/>
-      <x:c r="F25" s="30" t="n">
+      <x:c r="B25" s="25" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="31" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C26" s="32" t="s"/>
-      <x:c r="D26" s="32" t="s"/>
-      <x:c r="E26" s="32" t="s"/>
-      <x:c r="F26" s="33" t="n">
+      <x:c r="B26" s="28" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="30" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -1068,7 +1068,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1108,7 +1108,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1145,7 +1145,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1181,7 +1181,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
@@ -1217,7 +1217,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
@@ -1253,7 +1253,7 @@
         <x:v>37</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -1289,7 +1289,7 @@
         <x:v>37</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -1327,7 +1327,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="33.597656" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
@@ -1365,7 +1365,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>54</x:v>
       </x:c>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>EVALUATOR3 EDGE</x:t>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -22,15 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>EVALUATOR3 EDGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -549,7 +546,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -566,6 +563,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -624,7 +624,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -660,6 +660,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1034,20 +1038,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45809</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1070,435 +1074,435 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45832.3271846875</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45832.3272087963</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45832.3271846875</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45832.3272087963</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45832.3384320023</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45832.3384320023</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45825.0450396991</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45825.0450687153</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45825.0450396991</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45825.0450687153</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>45825.0561645718</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45827.2810495602</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45827.2810737963</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45827.2810495602</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45827.2810737963</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45827.2917648032</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>45826.310926169</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45826.3109462384</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45826.310926169</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45826.3109462384</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
+      <x:c r="K11" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45826.3168925232</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>45826.3168925232</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="F12" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="H12" s="17">
+        <x:v>45825.5009313657</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45825.5010245718</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45825.5009313657</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45825.5010245718</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="19">
         <x:v>45827.2850752315</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>37</x:v>
+      <x:c r="M12" s="15" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="B13" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="E13" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="H13" s="17">
+        <x:v>45825.1485242593</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45825.1485531713</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45825.1485242593</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45825.1485531713</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="19">
         <x:v>45825.1676413542</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M13" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
+      <x:c r="B14" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="D14" s="16" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="15" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="H14" s="17">
+        <x:v>45827.0419894213</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>45827.0420140278</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45827.0419894213</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>45827.0420140278</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="18">
+      <x:c r="L14" s="19">
         <x:v>45827.0460181713</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M14" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
+      <x:c r="B15" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="D15" s="16" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
+      <x:c r="E15" s="15" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="F15" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="H15" s="17">
+        <x:v>45827.193172581</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>44197</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>45827.193172581</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>44197</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L15" s="18">
+      <x:c r="L15" s="19">
         <x:v>45827.2195876273</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M15" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="19" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C18" s="20" t="s"/>
-      <x:c r="D18" s="20" t="s"/>
-      <x:c r="E18" s="21" t="s"/>
-      <x:c r="F18" s="21" t="s"/>
+      <x:c r="B18" s="20" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="22" t="s">
+      <x:c r="B19" s="23" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s"/>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="24" t="s">
-        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
+      <x:c r="B20" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
+      <x:c r="B21" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
+      <x:c r="B22" s="26" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="25" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="27" t="n">
+      <x:c r="B23" s="26" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="25" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C24" s="26" t="s"/>
-      <x:c r="D24" s="26" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="27" t="n">
+      <x:c r="B24" s="26" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="25" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C25" s="26" t="s"/>
-      <x:c r="D25" s="26" t="s"/>
-      <x:c r="E25" s="26" t="s"/>
-      <x:c r="F25" s="27" t="n">
+      <x:c r="B25" s="26" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="28" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C26" s="29" t="s"/>
-      <x:c r="D26" s="29" t="s"/>
-      <x:c r="E26" s="29" t="s"/>
-      <x:c r="F26" s="30" t="n">
+      <x:c r="B26" s="29" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C26" s="30" t="s"/>
+      <x:c r="D26" s="30" t="s"/>
+      <x:c r="E26" s="30" t="s"/>
+      <x:c r="F26" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -226,7 +226,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -266,14 +266,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -546,7 +538,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -557,16 +549,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -578,53 +567,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -659,87 +648,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1041,17 +1026,17 @@
       <x:c r="B5" s="12">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1074,435 +1059,435 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45832.3271846875</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45832.3272087963</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45832.3384320023</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45825.0450396991</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45825.0450687153</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45825.0561645718</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45827.2810495602</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45827.2810737963</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45827.2917648032</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45826.310926169</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45826.3109462384</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45826.3168925232</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45825.5009313657</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45825.5010245718</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45827.2850752315</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45825.1485242593</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45825.1485531713</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45825.1676413542</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>45827.0419894213</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>45827.0420140278</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>45827.0460181713</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>45827.193172581</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>45827.2195876273</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
+      <x:c r="B18" s="19" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
+      <x:c r="C18" s="20" t="s"/>
+      <x:c r="D18" s="20" t="s"/>
+      <x:c r="E18" s="21" t="s"/>
+      <x:c r="F18" s="21" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="s">
         <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+      <x:c r="B23" s="25" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+      <x:c r="B24" s="25" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
+      <x:c r="B25" s="25" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="29" t="s">
+      <x:c r="B26" s="28" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C26" s="30" t="s"/>
-      <x:c r="D26" s="30" t="s"/>
-      <x:c r="E26" s="30" t="s"/>
-      <x:c r="F26" s="31" t="n">
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="30" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR3-EDGE-evaluator-cache-serviceTracking-EVALUATOR3-EDGE-III-202501-202612.xlsx
@@ -69,54 +69,42 @@
     <x:t>Amateur</x:t>
   </x:si>
   <x:si>
-    <x:t>EDISSA ABASTAS AMANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manimpis, City Of San Fernando (Capital), Pampanga</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1023-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1061</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16854</x:t>
+    <x:t>JULIETA ROBLEDO AMANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1003-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1546810</x:t>
   </x:si>
   <x:si>
     <x:t>cashier3 edge</x:t>
   </x:si>
   <x:si>
-    <x:t>JULIETA ROBLEDO AMANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1003-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1546810</x:t>
+    <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RROC-RLM-ROIII-1005-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15135861</x:t>
   </x:si>
   <x:si>
     <x:t>Radiotelegraphy</x:t>
   </x:si>
   <x:si>
-    <x:t>ANGEL PANCHITO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1021-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1054</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1616</x:t>
-  </x:si>
-  <x:si>
     <x:t>EDWARD LANCE LORILLA</x:t>
   </x:si>
   <x:si>
@@ -133,39 +121,6 @@
   </x:si>
   <x:si>
     <x:t>MANUELITO TOLENTINO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Request for Blocking of IMEI and SIM of Lost/Stolen Mobile Phone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOHN ANTHONY AUSTRIA ROXAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30 bot 1 District 3, Pulong cacutud, Angeles City, Pampanga</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1011-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1434267</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RROC-RLM-ROIII-1005-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15135861</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
@@ -203,6 +158,51 @@
   </x:si>
   <x:si>
     <x:t>1234312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Request for Blocking of IMEI and SIM of Lost/Stolen Mobile Phone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOHN ANTHONY AUSTRIA ROXAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30 bot 1 District 3, Pulong cacutud, Angeles City, Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1011-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1434267</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEL PANCHITO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1021-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1054</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1616</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDISSA ABASTAS AMANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manimpis, City Of San Fernando (Capital), Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1023-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1061</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16854</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -1116,10 +1116,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>45832.3271846875</x:v>
+        <x:v>45825.0450396991</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>45832.3272087963</x:v>
+        <x:v>45825.0450687153</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
@@ -1128,7 +1128,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>45832.3384320023</x:v>
+        <x:v>45825.0561645718</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
@@ -1136,14 +1136,16 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
@@ -1152,19 +1154,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>45825.0450396991</x:v>
+        <x:v>45825.1485242593</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>45825.0450687153</x:v>
+        <x:v>45825.1485531713</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>50</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>45825.0561645718</x:v>
+        <x:v>45825.1676413542</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
@@ -1179,176 +1181,176 @@
       </x:c>
       <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>45827.2810495602</x:v>
+        <x:v>45826.310926169</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>45827.2810737963</x:v>
+        <x:v>45826.3109462384</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>45827.2917648032</x:v>
+        <x:v>45826.3168925232</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>45826.310926169</x:v>
+        <x:v>45827.0419894213</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>45826.3109462384</x:v>
+        <x:v>45827.0420140278</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>50</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>45826.3168925232</x:v>
+        <x:v>45827.0460181713</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s"/>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>45825.5009313657</x:v>
+        <x:v>45827.193172581</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>45825.5010245718</x:v>
+        <x:v>44197</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>18810</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>45827.2850752315</x:v>
+        <x:v>45827.2195876273</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s"/>
       <x:c r="E13" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>45825.1485242593</x:v>
+        <x:v>45825.5009313657</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>45825.1485531713</x:v>
+        <x:v>45825.5010245718</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>360</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>45825.1676413542</x:v>
+        <x:v>45827.2850752315</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s"/>
       <x:c r="E14" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45827.2810495602</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>45827.2810737963</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45827.0419894213</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>45827.0420140278</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
       <x:c r="L14" s="18">
-        <x:v>45827.0460181713</x:v>
+        <x:v>45827.2917648032</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>20</x:v>
@@ -1356,14 +1358,12 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
+      <x:c r="D15" s="15" t="s"/>
       <x:c r="E15" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
@@ -1374,19 +1374,19 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>45827.193172581</x:v>
+        <x:v>45832.3271846875</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>44197</x:v>
+        <x:v>45832.3272087963</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>18810</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>45827.2195876273</x:v>
+        <x:v>45832.3384320023</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>20</x:v>
@@ -1438,7 +1438,7 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="25" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="26" t="s"/>
       <x:c r="D22" s="26" t="s"/>
@@ -1449,7 +1449,7 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="25" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="26" t="s"/>
       <x:c r="D23" s="26" t="s"/>
@@ -1460,7 +1460,7 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="25" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C24" s="26" t="s"/>
       <x:c r="D24" s="26" t="s"/>
@@ -1471,7 +1471,7 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="25" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C25" s="26" t="s"/>
       <x:c r="D25" s="26" t="s"/>
